--- a/verification/cases/roundtrip/formula_stress_test/init.xlsx
+++ b/verification/cases/roundtrip/formula_stress_test/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23206"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{991D2587-D6AE-4ED8-8ED9-81B5584A0D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11740" yWindow="80" windowWidth="15420" windowHeight="19020" tabRatio="500" firstSheet="1" activeTab="4"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Database" sheetId="8" r:id="rId1"/>
@@ -18,11 +19,22 @@
     <sheet name="Statistical" sheetId="6" r:id="rId9"/>
     <sheet name="Text" sheetId="5" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -1581,7 +1593,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
@@ -1642,14 +1654,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1672,11 +1683,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Author" refreshedDate="41393.001978703702" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="6">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Author" refreshedDate="41393.001978703702" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="6" xr:uid="{00000000-000A-0000-FFFF-FFFF0D000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A24:E30" sheet="Database"/>
   </cacheSource>
@@ -1778,7 +1797,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="GPD" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="GPD" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
   <location ref="B32:O45" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
@@ -1918,6 +1937,11 @@
     <dataField name="Sum of Qux" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleMedium4" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
@@ -2242,19 +2266,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>378</v>
       </c>
@@ -2266,7 +2290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>379</v>
       </c>
@@ -2275,7 +2299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>380</v>
       </c>
@@ -2284,7 +2308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>381</v>
       </c>
@@ -2293,7 +2317,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>382</v>
       </c>
@@ -2302,7 +2326,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>383</v>
       </c>
@@ -2311,7 +2335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>384</v>
       </c>
@@ -2320,7 +2344,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>385</v>
       </c>
@@ -2329,7 +2353,7 @@
         <v>5.0579969684978394</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>386</v>
       </c>
@@ -2338,7 +2362,7 @@
         <v>4.3803538669838078</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>387</v>
       </c>
@@ -2351,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>388</v>
       </c>
@@ -2360,7 +2384,7 @@
         <v>12.333333333333343</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>389</v>
       </c>
@@ -2369,12 +2393,12 @@
         <v>8.2222222222222214</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>390</v>
       </c>
@@ -2383,12 +2407,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>437</v>
       </c>
@@ -2399,7 +2423,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>442</v>
       </c>
@@ -2410,17 +2434,17 @@
         <v>432</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>437</v>
       </c>
@@ -2437,7 +2461,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>442</v>
       </c>
@@ -2454,7 +2478,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>443</v>
       </c>
@@ -2471,7 +2495,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>444</v>
       </c>
@@ -2488,7 +2512,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>442</v>
       </c>
@@ -2505,7 +2529,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>443</v>
       </c>
@@ -2522,7 +2546,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>445</v>
       </c>
@@ -2539,15 +2563,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="8" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="7" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="33" spans="2:15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C33">
         <v>8</v>
       </c>
@@ -2588,8 +2612,8 @@
         <v>448</v>
       </c>
     </row>
-    <row r="34" spans="2:15">
-      <c r="B34" s="8" t="s">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B34" s="7" t="s">
         <v>447</v>
       </c>
       <c r="C34">
@@ -2611,295 +2635,199 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="2:15">
-      <c r="B35" s="9" t="s">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B35" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6">
+      <c r="I35">
         <v>9</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35">
         <v>9</v>
       </c>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6">
+      <c r="O35">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="2:15">
-      <c r="B36" s="10">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B36" s="9">
         <v>14</v>
       </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6">
+      <c r="I36">
         <v>9</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36">
         <v>9</v>
       </c>
-      <c r="K36" s="6"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6">
+      <c r="O36">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="2:15">
-      <c r="B37" s="9" t="s">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B37" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6">
+      <c r="E37">
         <v>8</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37">
         <v>8</v>
       </c>
-      <c r="G37" s="6">
+      <c r="G37">
         <v>10</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37">
         <v>10</v>
       </c>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6">
+      <c r="O37">
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="2:15">
-      <c r="B38" s="10">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B38" s="9">
         <v>8</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6">
+      <c r="E38">
         <v>8</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38">
         <v>8</v>
       </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6">
+      <c r="O38">
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="2:15">
-      <c r="B39" s="10">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B39" s="9">
         <v>12</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6">
+      <c r="G39">
         <v>10</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39">
         <v>10</v>
       </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6">
+      <c r="O39">
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="2:15">
-      <c r="B40" s="9" t="s">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B40" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="C40" s="6">
+      <c r="C40">
         <v>6</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40">
         <v>6</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6">
+      <c r="O40">
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="2:15">
-      <c r="B41" s="10">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B41" s="9">
         <v>9</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41">
         <v>6</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41">
         <v>6</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6">
+      <c r="O41">
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="2:15">
-      <c r="B42" s="9" t="s">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B42" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6">
+      <c r="K42">
         <v>10</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42">
         <v>10</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42">
         <v>14</v>
       </c>
-      <c r="N42" s="6">
+      <c r="N42">
         <v>14</v>
       </c>
-      <c r="O42" s="6">
+      <c r="O42">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:15">
-      <c r="B43" s="10">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B43" s="9">
         <v>15</v>
       </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="6"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6">
+      <c r="K43">
         <v>10</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43">
         <v>10</v>
       </c>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6">
+      <c r="O43">
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="2:15">
-      <c r="B44" s="10">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B44" s="9">
         <v>20</v>
       </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="6">
+      <c r="M44">
         <v>14</v>
       </c>
-      <c r="N44" s="6">
+      <c r="N44">
         <v>14</v>
       </c>
-      <c r="O44" s="6">
+      <c r="O44">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="2:15">
-      <c r="B45" s="9" t="s">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B45" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45">
         <v>6</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45">
         <v>6</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E45">
         <v>8</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45">
         <v>8</v>
       </c>
-      <c r="G45" s="6">
+      <c r="G45">
         <v>10</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45">
         <v>10</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45">
         <v>9</v>
       </c>
-      <c r="J45" s="6">
+      <c r="J45">
         <v>9</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45">
         <v>10</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45">
         <v>10</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45">
         <v>14</v>
       </c>
-      <c r="N45" s="6">
+      <c r="N45">
         <v>14</v>
       </c>
-      <c r="O45" s="6">
+      <c r="O45">
         <v>57</v>
       </c>
     </row>
@@ -2915,16 +2843,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>198</v>
       </c>
@@ -2945,7 +2873,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>200</v>
       </c>
@@ -2960,7 +2888,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>207</v>
       </c>
@@ -2972,7 +2900,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>208</v>
       </c>
@@ -2981,12 +2909,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>209</v>
       </c>
@@ -2998,7 +2926,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>213</v>
       </c>
@@ -3010,7 +2938,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>225</v>
       </c>
@@ -3022,12 +2950,12 @@
         <v>485</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>199</v>
       </c>
@@ -3039,7 +2967,7 @@
         <v>4.5670000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>203</v>
       </c>
@@ -3051,7 +2979,7 @@
         <v>0.12345679</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>223</v>
       </c>
@@ -3066,7 +2994,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>222</v>
       </c>
@@ -3078,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>226</v>
       </c>
@@ -3086,49 +3014,49 @@
         <f>VALUE(C17)</f>
         <v>12</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>195</v>
       </c>
       <c r="B20" t="str">
         <f>CHAR(C20)</f>
-        <v></v>
+        <v>ð</v>
       </c>
       <c r="C20">
         <v>240</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="16">
+    <row r="21" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>197</v>
       </c>
       <c r="B21">
         <f>CODE(C21)</f>
-        <v>240</v>
-      </c>
-      <c r="C21" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="16">
-      <c r="C22" s="16"/>
-    </row>
-    <row r="23" spans="1:5" ht="16">
+    <row r="22" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C22" s="15"/>
+    </row>
+    <row r="23" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>492</v>
       </c>
-      <c r="C23" s="16"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="C23" s="15"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>205</v>
       </c>
@@ -3143,7 +3071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>206</v>
       </c>
@@ -3152,7 +3080,7 @@
         <v>foo</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>210</v>
       </c>
@@ -3170,7 +3098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>211</v>
       </c>
@@ -3188,7 +3116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>217</v>
       </c>
@@ -3197,7 +3125,7 @@
         <v>qux</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>218</v>
       </c>
@@ -3206,16 +3134,16 @@
         <v>qux</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="16">
-      <c r="C30" s="16"/>
-    </row>
-    <row r="31" spans="1:5" ht="16">
+    <row r="30" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="C30" s="15"/>
+    </row>
+    <row r="31" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>493</v>
       </c>
-      <c r="C31" s="16"/>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="C31" s="15"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>201</v>
       </c>
@@ -3230,7 +3158,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>202</v>
       </c>
@@ -3239,7 +3167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>219</v>
       </c>
@@ -3248,7 +3176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>220</v>
       </c>
@@ -3257,7 +3185,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>498</v>
       </c>
@@ -3266,7 +3194,7 @@
         <v xml:space="preserve">badger badger badger badger badger badger badger badger badger badger badger badger MUSHROOM! MUSHROOM! </v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>196</v>
       </c>
@@ -3279,7 +3207,7 @@
         <v>_x0007_7_x0007_</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>216</v>
       </c>
@@ -3294,7 +3222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>214</v>
       </c>
@@ -3311,11 +3239,11 @@
       <c r="E40">
         <v>4</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="6" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>215</v>
       </c>
@@ -3324,7 +3252,7 @@
         <v>foo FOO baz qux</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>221</v>
       </c>
@@ -3345,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>224</v>
       </c>
@@ -3353,16 +3281,16 @@
         <f>TRIM(C43)</f>
         <v>there are two spaces here</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -3371,7 +3299,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>212</v>
       </c>
@@ -3383,7 +3311,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>204</v>
       </c>
@@ -3392,7 +3320,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>227</v>
       </c>
@@ -3416,20 +3344,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>391</v>
       </c>
@@ -3447,7 +3375,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>393</v>
       </c>
@@ -3455,15 +3383,15 @@
         <f>DATEVALUE(C3)</f>
         <v>25363</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>405</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="10">
         <f>TIME(C4,D4,E4)</f>
         <v>0.2565162037037037</v>
       </c>
@@ -3477,7 +3405,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>406</v>
       </c>
@@ -3485,38 +3413,38 @@
         <f>TIMEVALUE(C5)</f>
         <v>0.97482638888888884</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>403</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <f ca="1">NOW()</f>
-        <v>41399.879184143516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>46275.595223611112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>407</v>
       </c>
       <c r="B7" s="5">
         <f ca="1">TODAY()</f>
-        <v>41399</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="B8" s="11"/>
-    </row>
-    <row r="9" spans="1:5">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>459</v>
       </c>
-      <c r="B9" s="11"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="B9" s="10"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>412</v>
       </c>
@@ -3525,7 +3453,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>400</v>
       </c>
@@ -3534,7 +3462,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>394</v>
       </c>
@@ -3543,7 +3471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>398</v>
       </c>
@@ -3552,7 +3480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>399</v>
       </c>
@@ -3561,7 +3489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>404</v>
       </c>
@@ -3570,7 +3498,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>408</v>
       </c>
@@ -3579,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>409</v>
       </c>
@@ -3588,12 +3516,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>392</v>
       </c>
@@ -3612,7 +3540,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>395</v>
       </c>
@@ -3621,7 +3549,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>396</v>
       </c>
@@ -3633,7 +3561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>397</v>
       </c>
@@ -3645,7 +3573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>401</v>
       </c>
@@ -3654,7 +3582,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>402</v>
       </c>
@@ -3666,7 +3594,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>410</v>
       </c>
@@ -3678,7 +3606,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>411</v>
       </c>
@@ -3687,7 +3615,7 @@
         <v>41577</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>413</v>
       </c>
@@ -3708,11 +3636,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>178</v>
       </c>
@@ -3720,7 +3648,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>137</v>
       </c>
@@ -3739,7 +3667,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>138</v>
       </c>
@@ -3754,7 +3682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>139</v>
       </c>
@@ -3769,7 +3697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>140</v>
       </c>
@@ -3784,12 +3712,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>150</v>
       </c>
@@ -3798,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -3807,7 +3735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>152</v>
       </c>
@@ -3816,7 +3744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>153</v>
       </c>
@@ -3825,12 +3753,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -3848,7 +3776,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>141</v>
       </c>
@@ -3857,7 +3785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>142</v>
       </c>
@@ -3866,7 +3794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>143</v>
       </c>
@@ -3875,7 +3803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>146</v>
       </c>
@@ -3884,7 +3812,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>147</v>
       </c>
@@ -3893,7 +3821,7 @@
         <v>A</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>148</v>
       </c>
@@ -3902,7 +3830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>175</v>
       </c>
@@ -3911,7 +3839,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>176</v>
       </c>
@@ -3920,7 +3848,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>177</v>
       </c>
@@ -3929,7 +3857,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>155</v>
       </c>
@@ -3938,7 +3866,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>156</v>
       </c>
@@ -3947,7 +3875,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>157</v>
       </c>
@@ -3956,12 +3884,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -3970,7 +3898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>154</v>
       </c>
@@ -3979,12 +3907,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>144</v>
       </c>
@@ -3997,7 +3925,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>158</v>
       </c>
@@ -4010,7 +3938,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>159</v>
       </c>
@@ -4023,7 +3951,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>160</v>
       </c>
@@ -4036,7 +3964,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>161</v>
       </c>
@@ -4049,7 +3977,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>162</v>
       </c>
@@ -4062,7 +3990,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>163</v>
       </c>
@@ -4075,7 +4003,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>164</v>
       </c>
@@ -4088,7 +4016,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>165</v>
       </c>
@@ -4101,7 +4029,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>166</v>
       </c>
@@ -4114,7 +4042,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>167</v>
       </c>
@@ -4127,7 +4055,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>168</v>
       </c>
@@ -4140,7 +4068,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>169</v>
       </c>
@@ -4157,7 +4085,7 @@
         <v>4+6j</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>170</v>
       </c>
@@ -4170,7 +4098,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>171</v>
       </c>
@@ -4183,7 +4111,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>172</v>
       </c>
@@ -4196,7 +4124,7 @@
         <v>2+3j</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>173</v>
       </c>
@@ -4213,7 +4141,7 @@
         <v>4+5j</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>174</v>
       </c>
@@ -4242,20 +4170,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -4270,7 +4198,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -4279,7 +4207,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>82</v>
       </c>
@@ -4294,7 +4222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -4303,13 +4231,13 @@
         <v>5.2500000000000213E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>136</v>
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>87</v>
       </c>
@@ -4336,7 +4264,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -4369,7 +4297,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -4393,7 +4321,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -4414,7 +4342,7 @@
         <v>41365</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>113</v>
       </c>
@@ -4423,7 +4351,7 @@
         <v>-6.2115468608681113E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -4445,7 +4373,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -4462,7 +4390,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>83</v>
       </c>
@@ -4483,7 +4411,7 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -4501,7 +4429,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>88</v>
       </c>
@@ -4519,7 +4447,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>92</v>
       </c>
@@ -4537,7 +4465,7 @@
         <v>-1000</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -4546,7 +4474,7 @@
         <v>-2711.2340549268079</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -4555,7 +4483,7 @@
         <v>-2688.8271619108841</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -4573,7 +4501,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>104</v>
       </c>
@@ -4591,7 +4519,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -4615,7 +4543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -4624,7 +4552,7 @@
         <v>-934.10712342089789</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>130</v>
       </c>
@@ -4644,7 +4572,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -4656,7 +4584,7 @@
         <v>9.1399999999999995E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -4677,7 +4605,7 @@
         <v>98.45</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>110</v>
       </c>
@@ -4686,7 +4614,7 @@
         <v>9.141696292534264E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>100</v>
       </c>
@@ -4713,7 +4641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>114</v>
       </c>
@@ -4730,7 +4658,7 @@
       <c r="F32" s="2">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="G32" s="6">
+      <c r="G32">
         <v>95.042869999999994</v>
       </c>
       <c r="H32">
@@ -4740,7 +4668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -4761,7 +4689,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>101</v>
       </c>
@@ -4782,7 +4710,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>115</v>
       </c>
@@ -4794,7 +4722,7 @@
         <v>99.795000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>102</v>
       </c>
@@ -4818,7 +4746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -4838,14 +4766,14 @@
       <c r="G37" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37">
         <v>100.0123</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37">
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -4865,14 +4793,14 @@
       <c r="G38" s="3">
         <v>0.09</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38">
         <v>2</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -4881,7 +4809,7 @@
         <v>5.7356698139188387</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>64</v>
       </c>
@@ -4901,17 +4829,17 @@
       <c r="G40" s="3">
         <v>0.1</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40">
         <v>1000</v>
       </c>
-      <c r="I40" s="6">
-        <v>2</v>
-      </c>
-      <c r="J40" s="6">
+      <c r="I40">
+        <v>2</v>
+      </c>
+      <c r="J40">
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
@@ -4931,11 +4859,11 @@
       <c r="H41">
         <v>1000</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -4952,14 +4880,14 @@
       <c r="F42">
         <v>1000000</v>
       </c>
-      <c r="G42" s="6">
+      <c r="G42">
         <v>1014420</v>
       </c>
-      <c r="H42" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="H42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>105</v>
       </c>
@@ -4979,11 +4907,11 @@
       <c r="G43" s="2">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="H43" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
+      <c r="H43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -5019,7 +4947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>95</v>
       </c>
@@ -5042,7 +4970,7 @@
       <c r="H45" s="2">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45">
         <v>84.5</v>
       </c>
       <c r="J45">
@@ -5055,7 +4983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>96</v>
       </c>
@@ -5088,7 +5016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>97</v>
       </c>
@@ -5108,7 +5036,7 @@
       <c r="G47" s="2">
         <v>5.7500000000000002E-2</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47">
         <v>84.5</v>
       </c>
       <c r="I47">
@@ -5121,7 +5049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>68</v>
       </c>
@@ -5144,7 +5072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -5153,7 +5081,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -5162,7 +5090,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>71</v>
       </c>
@@ -5172,7 +5100,7 @@
       </c>
       <c r="C51" s="5"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>72</v>
       </c>
@@ -5181,7 +5109,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>73</v>
       </c>
@@ -5190,7 +5118,7 @@
         <v>39036</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>122</v>
       </c>
@@ -5207,7 +5135,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>76</v>
       </c>
@@ -5231,7 +5159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>77</v>
       </c>
@@ -5252,7 +5180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>106</v>
       </c>
@@ -5261,7 +5189,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>107</v>
       </c>
@@ -5282,7 +5210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>111</v>
       </c>
@@ -5309,7 +5237,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>66</v>
       </c>
@@ -5318,7 +5246,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>67</v>
       </c>
@@ -5357,11 +5285,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>414</v>
       </c>
@@ -5373,7 +5301,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>415</v>
       </c>
@@ -5386,19 +5314,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>416</v>
       </c>
       <c r="B3" t="str">
         <f ca="1">INFO(C3)</f>
-        <v>14.3</v>
+        <v>16.0</v>
       </c>
       <c r="C3" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>417</v>
       </c>
@@ -5407,7 +5335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>418</v>
       </c>
@@ -5416,7 +5344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>419</v>
       </c>
@@ -5425,7 +5353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>420</v>
       </c>
@@ -5437,7 +5365,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>421</v>
       </c>
@@ -5449,7 +5377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>422</v>
       </c>
@@ -5462,7 +5390,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>423</v>
       </c>
@@ -5474,7 +5402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>424</v>
       </c>
@@ -5482,11 +5410,11 @@
         <f>ISNUMBER(C11)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>425</v>
       </c>
@@ -5494,11 +5422,11 @@
         <f>ISODD(C12)</f>
         <v>1</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>426</v>
       </c>
@@ -5510,7 +5438,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>427</v>
       </c>
@@ -5522,7 +5450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>428</v>
       </c>
@@ -5534,7 +5462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>429</v>
       </c>
@@ -5543,7 +5471,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>430</v>
       </c>
@@ -5563,17 +5491,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>185</v>
       </c>
       <c r="B2" t="b">
@@ -5581,8 +5509,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>190</v>
       </c>
       <c r="B3" t="b">
@@ -5590,15 +5518,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="7"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="7" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>184</v>
       </c>
@@ -5613,7 +5541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>188</v>
       </c>
@@ -5622,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>189</v>
       </c>
@@ -5631,12 +5559,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>186</v>
       </c>
@@ -5651,7 +5579,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>187</v>
       </c>
@@ -5679,16 +5607,16 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>367</v>
       </c>
@@ -5697,7 +5625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>374</v>
       </c>
@@ -5706,7 +5634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>368</v>
       </c>
@@ -5715,7 +5643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>375</v>
       </c>
@@ -5724,7 +5652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>371</v>
       </c>
@@ -5736,7 +5664,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>365</v>
       </c>
@@ -5745,12 +5673,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>364</v>
       </c>
@@ -5759,7 +5687,7 @@
         <v>$B$2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>373</v>
       </c>
@@ -5777,13 +5705,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>479</v>
       </c>
-      <c r="B13" s="15"/>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="B13" s="14"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>366</v>
       </c>
@@ -5795,7 +5723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>369</v>
       </c>
@@ -5807,7 +5735,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>470</v>
       </c>
@@ -5822,7 +5750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>471</v>
       </c>
@@ -5837,7 +5765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>474</v>
       </c>
@@ -5849,7 +5777,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>475</v>
       </c>
@@ -5858,7 +5786,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>372</v>
       </c>
@@ -5870,7 +5798,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>377</v>
       </c>
@@ -5885,24 +5813,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>370</v>
       </c>
-      <c r="B23" s="14" t="str">
+      <c r="B23" s="13" t="str">
         <f>HYPERLINK("http://nig.gl","niggler")</f>
         <v>niggler</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="14"/>
-    </row>
-    <row r="25" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B24" s="13"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>376</v>
       </c>
@@ -5929,14 +5857,14 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
@@ -5971,7 +5899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5992,7 +5920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6001,7 +5929,7 @@
         <v>1.0471975511965976</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6010,7 +5938,7 @@
         <v>1.3169578969248166</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6019,7 +5947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6028,7 +5956,7 @@
         <v>0.52359877559829893</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6037,7 +5965,7 @@
         <v>1.4436354751788103</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6046,7 +5974,7 @@
         <v>1.1071487177940904</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6055,7 +5983,7 @@
         <v>1.1071487177940904</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -6064,7 +5992,7 @@
         <v>0.54930614433405489</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -6073,7 +6001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -6082,7 +6010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -6091,7 +6019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -6100,7 +6028,7 @@
         <v>-0.41614683654714241</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -6109,7 +6037,7 @@
         <v>3.7621956910836314</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -6118,7 +6046,7 @@
         <v>114.59155902616465</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>462</v>
       </c>
@@ -6130,7 +6058,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -6139,7 +6067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -6148,7 +6076,7 @@
         <v>7.3890560989306504</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -6157,7 +6085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6169,7 +6097,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -6178,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -6187,7 +6115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>280</v>
       </c>
@@ -6202,7 +6130,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -6214,7 +6142,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -6223,7 +6151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -6232,7 +6160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -6241,7 +6169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -6250,7 +6178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -6259,7 +6187,7 @@
         <v>2.1972245773362196</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -6268,7 +6196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -6277,7 +6205,7 @@
         <v>0.69897000433601886</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -6286,7 +6214,7 @@
         <v>-2.0000000000000018</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -6295,7 +6223,7 @@
         <v>-2.9999999999999973</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -6304,7 +6232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -6313,7 +6241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -6322,7 +6250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -6331,7 +6259,7 @@
         <v>2450448</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -6340,7 +6268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>321</v>
       </c>
@@ -6352,7 +6280,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -6361,7 +6289,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -6370,7 +6298,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -6379,7 +6307,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>38</v>
       </c>
@@ -6388,7 +6316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -6397,25 +6325,25 @@
         <v>8.7266462599716474E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>40</v>
       </c>
       <c r="B46">
         <f ca="1">RAND()</f>
-        <v>0.16104002347522117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>0.3778286111083472</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>41</v>
       </c>
       <c r="B47">
         <f ca="1">RANDBETWEEN(D1,E2)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>42</v>
       </c>
@@ -6428,7 +6356,7 @@
         <v>II</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>43</v>
       </c>
@@ -6437,7 +6365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>44</v>
       </c>
@@ -6446,7 +6374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -6455,7 +6383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -6464,7 +6392,7 @@
         <v>2.928421387459129E+23</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -6473,7 +6401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -6482,7 +6410,7 @@
         <v>-0.95892427466313845</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -6491,7 +6419,7 @@
         <v>201.71315737027922</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>50</v>
       </c>
@@ -6500,7 +6428,7 @@
         <v>1.7320508075688772</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>51</v>
       </c>
@@ -6509,7 +6437,7 @@
         <v>2.5066282746310002</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>335</v>
       </c>
@@ -6530,7 +6458,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>52</v>
       </c>
@@ -6539,7 +6467,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>53</v>
       </c>
@@ -6556,7 +6484,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -6569,7 +6497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -6578,7 +6506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -6591,7 +6519,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -6604,7 +6532,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -6613,7 +6541,7 @@
         <v>-88</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -6622,7 +6550,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>60</v>
       </c>
@@ -6631,7 +6559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>61</v>
       </c>
@@ -6640,7 +6568,7 @@
         <v>-3.3805150062465859</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>62</v>
       </c>
@@ -6649,7 +6577,7 @@
         <v>0.99505475368673058</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>63</v>
       </c>
@@ -6670,20 +6598,20 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J144"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -6704,7 +6632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>234</v>
       </c>
@@ -6722,7 +6650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>235</v>
       </c>
@@ -6740,7 +6668,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>236</v>
       </c>
@@ -6758,7 +6686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>237</v>
       </c>
@@ -6779,7 +6707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>238</v>
       </c>
@@ -6800,7 +6728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -6821,7 +6749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>240</v>
       </c>
@@ -6836,7 +6764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>241</v>
       </c>
@@ -6845,7 +6773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>242</v>
       </c>
@@ -6863,7 +6791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>243</v>
       </c>
@@ -6872,7 +6800,7 @@
         <v>0.65996322969428256</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>244</v>
       </c>
@@ -6881,7 +6809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>245</v>
       </c>
@@ -6890,7 +6818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>248</v>
       </c>
@@ -6908,7 +6836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>249</v>
       </c>
@@ -6926,7 +6854,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>250</v>
       </c>
@@ -6944,7 +6872,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>260</v>
       </c>
@@ -6962,7 +6890,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>262</v>
       </c>
@@ -6980,7 +6908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>263</v>
       </c>
@@ -6998,7 +6926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>264</v>
       </c>
@@ -7019,7 +6947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>265</v>
       </c>
@@ -7028,7 +6956,7 @@
         <v>0.46475800154489</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>266</v>
       </c>
@@ -7037,7 +6965,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>267</v>
       </c>
@@ -7046,7 +6974,7 @@
         <v>1.0000000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>269</v>
       </c>
@@ -7064,7 +6992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>270</v>
       </c>
@@ -7073,7 +7001,7 @@
         <v>5.0000000000000009</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>271</v>
       </c>
@@ -7085,7 +7013,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>272</v>
       </c>
@@ -7094,7 +7022,7 @@
         <v>0.50000000000000011</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>276</v>
       </c>
@@ -7115,7 +7043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>277</v>
       </c>
@@ -7124,7 +7052,7 @@
         <v>3.9999999999999991</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>278</v>
       </c>
@@ -7133,7 +7061,7 @@
         <v>0.38494001106330422</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>279</v>
       </c>
@@ -7142,7 +7070,7 @@
         <v>3.9999999999999991</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>285</v>
       </c>
@@ -7166,7 +7094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>286</v>
       </c>
@@ -7187,7 +7115,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>292</v>
       </c>
@@ -7205,7 +7133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>293</v>
       </c>
@@ -7226,7 +7154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>294</v>
       </c>
@@ -7235,7 +7163,7 @@
         <v>0.99999999999999867</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>295</v>
       </c>
@@ -7244,7 +7172,7 @@
         <v>0.34457825838967576</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>304</v>
       </c>
@@ -7265,7 +7193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>305</v>
       </c>
@@ -7283,7 +7211,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>306</v>
       </c>
@@ -7304,7 +7232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>307</v>
       </c>
@@ -7313,7 +7241,7 @@
         <v>8.8817841970012523E-16</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>308</v>
       </c>
@@ -7328,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>309</v>
       </c>
@@ -7337,7 +7265,7 @@
         <v>2.9999999999999969</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>310</v>
       </c>
@@ -7346,7 +7274,7 @@
         <v>0.63055865981823644</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>311</v>
       </c>
@@ -7355,7 +7283,7 @@
         <v>8.8817841970012523E-16</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>312</v>
       </c>
@@ -7367,7 +7295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>313</v>
       </c>
@@ -7376,7 +7304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>322</v>
       </c>
@@ -7394,7 +7322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>323</v>
       </c>
@@ -7412,7 +7340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>343</v>
       </c>
@@ -7430,7 +7358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>344</v>
       </c>
@@ -7439,7 +7367,7 @@
         <v>1.9942126131992539E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>345</v>
       </c>
@@ -7448,7 +7376,7 @@
         <v>9.9710630659962697E-3</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>346</v>
       </c>
@@ -7457,7 +7385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>347</v>
       </c>
@@ -7466,7 +7394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>349</v>
       </c>
@@ -7484,7 +7412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>350</v>
       </c>
@@ -7493,7 +7421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>360</v>
       </c>
@@ -7514,7 +7442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>361</v>
       </c>
@@ -7535,12 +7463,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>228</v>
       </c>
@@ -7573,7 +7501,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>229</v>
       </c>
@@ -7606,7 +7534,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>230</v>
       </c>
@@ -7639,7 +7567,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>231</v>
       </c>
@@ -7672,7 +7600,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>232</v>
       </c>
@@ -7705,7 +7633,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>251</v>
       </c>
@@ -7732,7 +7660,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>252</v>
       </c>
@@ -7762,7 +7690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>253</v>
       </c>
@@ -7792,7 +7720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>254</v>
       </c>
@@ -7822,7 +7750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>255</v>
       </c>
@@ -7855,7 +7783,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>256</v>
       </c>
@@ -7888,7 +7816,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>257</v>
       </c>
@@ -7918,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>258</v>
       </c>
@@ -7948,7 +7876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>259</v>
       </c>
@@ -7957,7 +7885,7 @@
         <v>43.6</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>261</v>
       </c>
@@ -7987,7 +7915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>282</v>
       </c>
@@ -8017,7 +7945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>284</v>
       </c>
@@ -8047,7 +7975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>288</v>
       </c>
@@ -8077,7 +8005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>289</v>
       </c>
@@ -8107,7 +8035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>296</v>
       </c>
@@ -8137,7 +8065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>297</v>
       </c>
@@ -8167,37 +8095,37 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>298</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="16">
         <f>MEDIAN(C83:I83)</f>
         <v>4</v>
       </c>
-      <c r="C83" s="17">
-        <v>1</v>
-      </c>
-      <c r="D83" s="17">
-        <v>2</v>
-      </c>
-      <c r="E83" s="17">
+      <c r="C83" s="16">
+        <v>1</v>
+      </c>
+      <c r="D83" s="16">
+        <v>2</v>
+      </c>
+      <c r="E83" s="16">
         <v>4</v>
       </c>
-      <c r="F83" s="17">
+      <c r="F83" s="16">
         <v>8</v>
       </c>
-      <c r="G83" s="17">
+      <c r="G83" s="16">
         <v>16</v>
       </c>
-      <c r="H83" s="17">
+      <c r="H83" s="16">
         <v>32</v>
       </c>
-      <c r="I83" s="17">
+      <c r="I83" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>299</v>
       </c>
@@ -8205,29 +8133,29 @@
         <f>MIN(C84:I84)</f>
         <v>1</v>
       </c>
-      <c r="C84" s="17">
-        <v>1</v>
-      </c>
-      <c r="D84" s="17">
-        <v>2</v>
-      </c>
-      <c r="E84" s="17">
+      <c r="C84" s="16">
+        <v>1</v>
+      </c>
+      <c r="D84" s="16">
+        <v>2</v>
+      </c>
+      <c r="E84" s="16">
         <v>4</v>
       </c>
-      <c r="F84" s="17">
+      <c r="F84" s="16">
         <v>8</v>
       </c>
-      <c r="G84" s="17">
+      <c r="G84" s="16">
         <v>16</v>
       </c>
-      <c r="H84" s="17">
+      <c r="H84" s="16">
         <v>32</v>
       </c>
-      <c r="I84" s="17">
+      <c r="I84" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>300</v>
       </c>
@@ -8235,29 +8163,29 @@
         <f>MINA(C85:I85)</f>
         <v>1</v>
       </c>
-      <c r="C85" s="17">
-        <v>1</v>
-      </c>
-      <c r="D85" s="17">
-        <v>2</v>
-      </c>
-      <c r="E85" s="17">
+      <c r="C85" s="16">
+        <v>1</v>
+      </c>
+      <c r="D85" s="16">
+        <v>2</v>
+      </c>
+      <c r="E85" s="16">
         <v>4</v>
       </c>
-      <c r="F85" s="17">
+      <c r="F85" s="16">
         <v>8</v>
       </c>
-      <c r="G85" s="17">
+      <c r="G85" s="16">
         <v>16</v>
       </c>
-      <c r="H85" s="17">
+      <c r="H85" s="16">
         <v>32</v>
       </c>
-      <c r="I85" s="17">
+      <c r="I85" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>301</v>
       </c>
@@ -8265,29 +8193,29 @@
         <f>MODE(C86:I86)</f>
         <v>16</v>
       </c>
-      <c r="C86" s="17">
-        <v>1</v>
-      </c>
-      <c r="D86" s="17">
-        <v>2</v>
-      </c>
-      <c r="E86" s="17">
+      <c r="C86" s="16">
+        <v>1</v>
+      </c>
+      <c r="D86" s="16">
+        <v>2</v>
+      </c>
+      <c r="E86" s="16">
         <v>4</v>
       </c>
-      <c r="F86" s="17">
+      <c r="F86" s="16">
         <v>8</v>
       </c>
-      <c r="G86" s="17">
+      <c r="G86" s="16">
         <v>16</v>
       </c>
-      <c r="H86" s="17">
+      <c r="H86" s="16">
         <v>16</v>
       </c>
-      <c r="I86" s="17">
+      <c r="I86" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>302</v>
       </c>
@@ -8295,29 +8223,29 @@
         <f>_xlfn.MODE.MULT(C87:I87)</f>
         <v>8</v>
       </c>
-      <c r="C87" s="17">
-        <v>1</v>
-      </c>
-      <c r="D87" s="17">
-        <v>2</v>
-      </c>
-      <c r="E87" s="17">
+      <c r="C87" s="16">
+        <v>1</v>
+      </c>
+      <c r="D87" s="16">
+        <v>2</v>
+      </c>
+      <c r="E87" s="16">
         <v>4</v>
       </c>
-      <c r="F87" s="17">
+      <c r="F87" s="16">
         <v>8</v>
       </c>
-      <c r="G87" s="17">
+      <c r="G87" s="16">
         <v>8</v>
       </c>
-      <c r="H87" s="17">
+      <c r="H87" s="16">
         <v>32</v>
       </c>
-      <c r="I87" s="17">
+      <c r="I87" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>303</v>
       </c>
@@ -8326,7 +8254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>315</v>
       </c>
@@ -8356,7 +8284,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>316</v>
       </c>
@@ -8386,7 +8314,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>317</v>
       </c>
@@ -8416,7 +8344,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>318</v>
       </c>
@@ -8446,7 +8374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>319</v>
       </c>
@@ -8476,7 +8404,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>320</v>
       </c>
@@ -8506,7 +8434,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>325</v>
       </c>
@@ -8536,7 +8464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>326</v>
       </c>
@@ -8566,7 +8494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>327</v>
       </c>
@@ -8596,7 +8524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>328</v>
       </c>
@@ -8622,11 +8550,11 @@
       <c r="H98">
         <v>32</v>
       </c>
-      <c r="I98" s="17" t="s">
+      <c r="I98" s="16" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>329</v>
       </c>
@@ -8656,7 +8584,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>330</v>
       </c>
@@ -8686,7 +8614,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>332</v>
       </c>
@@ -8713,7 +8641,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>334</v>
       </c>
@@ -8743,7 +8671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>336</v>
       </c>
@@ -8773,7 +8701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>337</v>
       </c>
@@ -8803,7 +8731,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>338</v>
       </c>
@@ -8833,7 +8761,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>339</v>
       </c>
@@ -8863,7 +8791,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>340</v>
       </c>
@@ -8893,7 +8821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>341</v>
       </c>
@@ -8923,12 +8851,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>354</v>
       </c>
@@ -8958,7 +8886,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>355</v>
       </c>
@@ -8988,7 +8916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>356</v>
       </c>
@@ -9018,7 +8946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>357</v>
       </c>
@@ -9048,7 +8976,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>358</v>
       </c>
@@ -9078,7 +9006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>359</v>
       </c>
@@ -9108,12 +9036,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>246</v>
       </c>
@@ -9140,7 +9068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>247</v>
       </c>
@@ -9167,7 +9095,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>268</v>
       </c>
@@ -9176,7 +9104,7 @@
         <v>0.31774423874816832</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>275</v>
       </c>
@@ -9185,7 +9113,7 @@
         <v>0.31774423874816832</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>348</v>
       </c>
@@ -9200,7 +9128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>353</v>
       </c>
@@ -9209,7 +9137,7 @@
         <v>0.55113345694457505</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>362</v>
       </c>
@@ -9239,7 +9167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>363</v>
       </c>
@@ -9251,12 +9179,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>273</v>
       </c>
@@ -9286,7 +9214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>274</v>
       </c>
@@ -9313,7 +9241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>283</v>
       </c>
@@ -9340,7 +9268,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>287</v>
       </c>
@@ -9349,7 +9277,7 @@
         <v>0.20000000000000018</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>324</v>
       </c>
@@ -9364,7 +9292,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>314</v>
       </c>
@@ -9373,7 +9301,7 @@
         <v>0.86469929256476752</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>331</v>
       </c>
@@ -9382,7 +9310,7 @@
         <v>0.97142857142857142</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>333</v>
       </c>
@@ -9391,7 +9319,7 @@
         <v>1.9428571428571428</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>342</v>
       </c>
@@ -9400,7 +9328,7 @@
         <v>0.69693205243716838</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
         <v>512</v>
       </c>
@@ -9408,7 +9336,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>290</v>
       </c>
@@ -9431,7 +9359,7 @@
         <v>1.8339088200571829</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>291</v>
       </c>
@@ -9452,7 +9380,7 @@
         <v>0.1997490475347993</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>351</v>
       </c>
@@ -9473,7 +9401,7 @@
         <v>0.21456489602231923</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D141">
         <v>135.99999999999994</v>
       </c>
@@ -9487,7 +9415,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D142">
         <v>66.05714285714285</v>
       </c>
@@ -9501,7 +9429,7 @@
         <v>0.18415237842027465</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>351</v>
       </c>
